--- a/artfynd/A 2680-2026 artfynd.xlsx
+++ b/artfynd/A 2680-2026 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>2543434</v>
       </c>
       <c r="B2" t="n">
-        <v>105122</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>108194</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>641218.4754501225</v>
+        <v>641218</v>
       </c>
       <c r="R2" t="n">
-        <v>6554015.933237873</v>
+        <v>6554016</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +743,9 @@
           <t>1975-06-23</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1975-06-23</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,32 +777,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>3310193</v>
+        <v>2749172</v>
       </c>
       <c r="B3" t="n">
-        <v>103087</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110078</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221101</v>
+        <v>220299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Springkorn</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Impatiens noli-tangere</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -832,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>641218.4754501225</v>
+        <v>641218</v>
       </c>
       <c r="R3" t="n">
-        <v>6554015.933237873</v>
+        <v>6554016</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -865,19 +845,9 @@
           <t>1975-06-23</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1975-06-23</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,32 +879,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2749172</v>
+        <v>3310193</v>
       </c>
       <c r="B4" t="n">
-        <v>106963</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106061</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220299</v>
+        <v>221101</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Springkorn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Impatiens noli-tangere</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -949,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>641218.4754501225</v>
+        <v>641218</v>
       </c>
       <c r="R4" t="n">
-        <v>6554015.933237873</v>
+        <v>6554016</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -982,19 +947,9 @@
           <t>1975-06-23</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>1975-06-23</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,16 +984,11 @@
         <v>3763329</v>
       </c>
       <c r="B5" t="n">
-        <v>99397</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102241</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1066,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>641218.4754501225</v>
+        <v>641218</v>
       </c>
       <c r="R5" t="n">
-        <v>6554015.933237873</v>
+        <v>6554016</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1099,19 +1049,9 @@
           <t>1975-06-23</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>1975-06-23</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1146,12 +1086,7 @@
         <v>5320889</v>
       </c>
       <c r="B6" t="n">
-        <v>98430</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101228</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>641218.4754501225</v>
+        <v>641218</v>
       </c>
       <c r="R6" t="n">
-        <v>6554015.933237873</v>
+        <v>6554016</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1216,19 +1151,9 @@
           <t>1975-06-23</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>1975-06-23</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 2680-2026 artfynd.xlsx
+++ b/artfynd/A 2680-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2543434</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2749172</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3310193</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3763329</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,8 +1207,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5320889</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>